--- a/api/templates/export/supplies-by-site-and-consumable/es.xlsx
+++ b/api/templates/export/supplies-by-site-and-consumable/es.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\export\supplies-by-site-and-consumable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71ED3809-5F5B-4B56-B006-0E14EE84FDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D4688D-7C41-41FE-93EF-9B3B8C225849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -160,16 +160,16 @@
     <t>Días de Stock Restantes</t>
   </si>
   <si>
-    <t>Stock a Ser Desperdiciado</t>
-  </si>
-  <si>
-    <t>&lt;toBeWasted&gt;</t>
-  </si>
-  <si>
     <t>&lt;daysStockLeft&gt;</t>
   </si>
   <si>
     <t>&lt;dailyConsumptionRate&gt;</t>
+  </si>
+  <si>
+    <t>&lt;projectedWaste&gt;</t>
+  </si>
+  <si>
+    <t>Desperdicio de Stock Projectado</t>
   </si>
 </sst>
 </file>
@@ -303,7 +303,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -335,6 +335,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -798,7 +801,7 @@
         <v>43</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -812,13 +815,13 @@
         <v>34</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
